--- a/AAII_Financials/Yearly/XYIGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XYIGY_YR_FIN.xlsx
@@ -2905,7 +2905,7 @@
         <v>214500</v>
       </c>
       <c r="E83" s="3">
-        <v>204100</v>
+        <v>198200</v>
       </c>
       <c r="F83" s="3">
         <v>192700</v>
